--- a/Less01/01magazzino.xlsx
+++ b/Less01/01magazzino.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Il mio Drive\Lesson\FITSTIC\_OLD\FITSTIC_SALESIANI\Corso26Analisi\Less01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2ED88C-22FA-431F-84A1-D8EB575BD3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9DF3EC-4E42-4B38-BB99-463DA295B24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{53ECDA96-0164-449F-A97E-2FF91888DEDE}"/>
+    <workbookView xWindow="4692" yWindow="1536" windowWidth="14916" windowHeight="12144" xr2:uid="{53ECDA96-0164-449F-A97E-2FF91888DEDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Prodotti" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Prodotti!$I$1:$J$1</definedName>
-    <definedName name="Prodotti">Prodotti!$A$1:$A$26</definedName>
+    <definedName name="Prodotti">Prodotti!$B$1:$B$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -583,10 +583,10 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>13</v>
@@ -614,12 +614,12 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="str">
+        <f>VLOOKUP(B2,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="str">
-        <f>VLOOKUP(A2,$I$1:$J$26,2,FALSE)</f>
-        <v>Compressori</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -644,17 +644,17 @@
         <v>Aspiratori</v>
       </c>
       <c r="M2" s="6">
-        <f>SUMIF($B$2:$B$201,L2,$C$2:$C$201)</f>
+        <f>SUMIF($A$2:$A$201,L2,$C$2:$C$201)</f>
         <v>1976</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="str">
+        <f>VLOOKUP(B3,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" t="str">
-        <f t="shared" ref="B3:B66" si="0">VLOOKUP(A3,$I$1:$J$26,2,FALSE)</f>
-        <v>Compressori</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -678,17 +678,17 @@
         <v>Compressori</v>
       </c>
       <c r="M3" s="6">
-        <f t="shared" ref="M3:M5" si="1">SUMIF($B$2:$B$201,L3,$C$2:$C$201)</f>
+        <f>SUMIF($A$2:$A$201,L3,$C$2:$C$201)</f>
         <v>2536</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="str">
+        <f>VLOOKUP(B4,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -712,17 +712,17 @@
         <v>Pompe</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" si="1"/>
+        <f>SUMIF($A$2:$A$201,L4,$C$2:$C$201)</f>
         <v>3704</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="str">
+        <f>VLOOKUP(B5,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -746,17 +746,17 @@
         <v>Trapani</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="1"/>
+        <f>SUMIF($A$2:$A$201,L5,$C$2:$C$201)</f>
         <v>864</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="str">
+        <f>VLOOKUP(B6,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -778,12 +778,12 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="str">
+        <f>VLOOKUP(B7,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
-      </c>
-      <c r="B7" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -805,12 +805,12 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="str">
+        <f>VLOOKUP(B8,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -832,12 +832,12 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="str">
+        <f>VLOOKUP(B9,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
-      </c>
-      <c r="B9" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -859,12 +859,12 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="str">
+        <f>VLOOKUP(B10,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -886,12 +886,12 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="str">
+        <f>VLOOKUP(B11,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C11">
         <v>14</v>
@@ -913,12 +913,12 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="str">
+        <f>VLOOKUP(B12,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C12">
         <v>14</v>
@@ -940,12 +940,12 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" t="str">
+        <f>VLOOKUP(B13,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C13">
         <v>14</v>
@@ -967,12 +967,12 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" t="str">
+        <f>VLOOKUP(B14,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B14" t="s">
         <v>28</v>
-      </c>
-      <c r="B14" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C14">
         <v>14</v>
@@ -994,12 +994,12 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" t="str">
+        <f>VLOOKUP(B15,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B15" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -1021,12 +1021,12 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" t="str">
+        <f>VLOOKUP(B16,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B16" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -1048,12 +1048,12 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" t="str">
+        <f>VLOOKUP(B17,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B17" t="s">
         <v>28</v>
-      </c>
-      <c r="B17" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C17">
         <v>14</v>
@@ -1075,12 +1075,12 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" t="str">
+        <f>VLOOKUP(B18,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B18" t="s">
         <v>22</v>
-      </c>
-      <c r="B18" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C18">
         <v>22</v>
@@ -1102,12 +1102,12 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" t="str">
+        <f>VLOOKUP(B19,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B19" t="s">
         <v>22</v>
-      </c>
-      <c r="B19" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C19">
         <v>22</v>
@@ -1129,12 +1129,12 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" t="str">
+        <f>VLOOKUP(B20,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B20" t="s">
         <v>22</v>
-      </c>
-      <c r="B20" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C20">
         <v>22</v>
@@ -1156,12 +1156,12 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" t="str">
+        <f>VLOOKUP(B21,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B21" t="s">
         <v>22</v>
-      </c>
-      <c r="B21" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C21">
         <v>22</v>
@@ -1183,12 +1183,12 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" t="str">
+        <f>VLOOKUP(B22,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B22" t="s">
         <v>22</v>
-      </c>
-      <c r="B22" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C22">
         <v>22</v>
@@ -1210,12 +1210,12 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" t="str">
+        <f>VLOOKUP(B23,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B23" t="s">
         <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -1237,12 +1237,12 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" t="str">
+        <f>VLOOKUP(B24,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B24" t="s">
         <v>22</v>
-      </c>
-      <c r="B24" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C24">
         <v>22</v>
@@ -1264,12 +1264,12 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" t="str">
+        <f>VLOOKUP(B25,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B25" t="s">
         <v>22</v>
-      </c>
-      <c r="B25" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C25">
         <v>22</v>
@@ -1291,12 +1291,12 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" t="str">
+        <f>VLOOKUP(B26,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B26" t="s">
         <v>5</v>
-      </c>
-      <c r="B26" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C26">
         <v>26</v>
@@ -1318,12 +1318,12 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" t="str">
+        <f>VLOOKUP(B27,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B27" t="s">
         <v>5</v>
-      </c>
-      <c r="B27" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C27">
         <v>26</v>
@@ -1339,12 +1339,12 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" t="str">
+        <f>VLOOKUP(B28,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B28" t="s">
         <v>5</v>
-      </c>
-      <c r="B28" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C28">
         <v>26</v>
@@ -1360,12 +1360,12 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" t="str">
+        <f>VLOOKUP(B29,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B29" t="s">
         <v>5</v>
-      </c>
-      <c r="B29" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C29">
         <v>26</v>
@@ -1381,12 +1381,12 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" t="str">
+        <f>VLOOKUP(B30,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B30" t="s">
         <v>5</v>
-      </c>
-      <c r="B30" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -1402,12 +1402,12 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" t="str">
+        <f>VLOOKUP(B31,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B31" t="s">
         <v>5</v>
-      </c>
-      <c r="B31" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C31">
         <v>26</v>
@@ -1423,12 +1423,12 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" t="str">
+        <f>VLOOKUP(B32,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B32" t="s">
         <v>5</v>
-      </c>
-      <c r="B32" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C32">
         <v>26</v>
@@ -1444,12 +1444,12 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" t="str">
+        <f>VLOOKUP(B33,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B33" t="s">
         <v>5</v>
-      </c>
-      <c r="B33" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C33">
         <v>26</v>
@@ -1465,12 +1465,12 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" t="str">
+        <f>VLOOKUP(B34,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B34" t="s">
         <v>23</v>
-      </c>
-      <c r="B34" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C34">
         <v>28</v>
@@ -1486,12 +1486,12 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" t="str">
+        <f>VLOOKUP(B35,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B35" t="s">
         <v>23</v>
-      </c>
-      <c r="B35" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C35">
         <v>28</v>
@@ -1507,12 +1507,12 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" t="str">
+        <f>VLOOKUP(B36,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B36" t="s">
         <v>23</v>
-      </c>
-      <c r="B36" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C36">
         <v>28</v>
@@ -1528,12 +1528,12 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" t="str">
+        <f>VLOOKUP(B37,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B37" t="s">
         <v>23</v>
-      </c>
-      <c r="B37" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C37">
         <v>28</v>
@@ -1549,12 +1549,12 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" t="str">
+        <f>VLOOKUP(B38,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B38" t="s">
         <v>23</v>
-      </c>
-      <c r="B38" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C38">
         <v>28</v>
@@ -1570,12 +1570,12 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" t="str">
+        <f>VLOOKUP(B39,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B39" t="s">
         <v>23</v>
-      </c>
-      <c r="B39" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C39">
         <v>28</v>
@@ -1591,12 +1591,12 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" t="str">
+        <f>VLOOKUP(B40,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B40" t="s">
         <v>23</v>
-      </c>
-      <c r="B40" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C40">
         <v>28</v>
@@ -1612,12 +1612,12 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" t="str">
+        <f>VLOOKUP(B41,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B41" t="s">
         <v>23</v>
-      </c>
-      <c r="B41" t="str">
-        <f t="shared" si="0"/>
-        <v>Pompe</v>
       </c>
       <c r="C41">
         <v>28</v>
@@ -1633,12 +1633,12 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A42" t="str">
+        <f>VLOOKUP(B42,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B42" t="s">
+        <v>20</v>
       </c>
       <c r="C42">
         <v>28</v>
@@ -1654,12 +1654,12 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B43" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A43" t="str">
+        <f>VLOOKUP(B43,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B43" t="s">
+        <v>20</v>
       </c>
       <c r="C43">
         <v>28</v>
@@ -1675,12 +1675,12 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A44" t="str">
+        <f>VLOOKUP(B44,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B44" t="s">
+        <v>20</v>
       </c>
       <c r="C44">
         <v>28</v>
@@ -1696,12 +1696,12 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A45" t="str">
+        <f>VLOOKUP(B45,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
       </c>
       <c r="C45">
         <v>28</v>
@@ -1717,12 +1717,12 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A46" t="str">
+        <f>VLOOKUP(B46,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B46" t="s">
+        <v>20</v>
       </c>
       <c r="C46">
         <v>28</v>
@@ -1738,12 +1738,12 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A47" t="str">
+        <f>VLOOKUP(B47,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
       </c>
       <c r="C47">
         <v>28</v>
@@ -1759,12 +1759,12 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B48" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A48" t="str">
+        <f>VLOOKUP(B48,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B48" t="s">
+        <v>20</v>
       </c>
       <c r="C48">
         <v>28</v>
@@ -1780,12 +1780,12 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>20</v>
-      </c>
-      <c r="B49" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
+      <c r="A49" t="str">
+        <f>VLOOKUP(B49,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
       </c>
       <c r="C49">
         <v>28</v>
@@ -1801,12 +1801,12 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" t="str">
+        <f>VLOOKUP(B50,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B50" t="s">
         <v>0</v>
-      </c>
-      <c r="B50" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C50">
         <v>32</v>
@@ -1822,12 +1822,12 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" t="str">
+        <f>VLOOKUP(B51,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B51" t="s">
         <v>0</v>
-      </c>
-      <c r="B51" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C51">
         <v>32</v>
@@ -1843,12 +1843,12 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" t="str">
+        <f>VLOOKUP(B52,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B52" t="s">
         <v>0</v>
-      </c>
-      <c r="B52" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C52">
         <v>32</v>
@@ -1864,12 +1864,12 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" t="str">
+        <f>VLOOKUP(B53,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B53" t="s">
         <v>0</v>
-      </c>
-      <c r="B53" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C53">
         <v>32</v>
@@ -1885,12 +1885,12 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" t="str">
+        <f>VLOOKUP(B54,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B54" t="s">
         <v>0</v>
-      </c>
-      <c r="B54" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C54">
         <v>32</v>
@@ -1906,12 +1906,12 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" t="str">
+        <f>VLOOKUP(B55,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B55" t="s">
         <v>0</v>
-      </c>
-      <c r="B55" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C55">
         <v>32</v>
@@ -1927,12 +1927,12 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" t="str">
+        <f>VLOOKUP(B56,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B56" t="s">
         <v>0</v>
-      </c>
-      <c r="B56" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C56">
         <v>32</v>
@@ -1948,12 +1948,12 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" t="str">
+        <f>VLOOKUP(B57,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B57" t="s">
         <v>0</v>
-      </c>
-      <c r="B57" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C57">
         <v>32</v>
@@ -1969,12 +1969,12 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" t="str">
+        <f>VLOOKUP(B58,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B58" t="s">
         <v>19</v>
-      </c>
-      <c r="B58" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C58">
         <v>32</v>
@@ -1990,12 +1990,12 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" t="str">
+        <f>VLOOKUP(B59,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B59" t="s">
         <v>19</v>
-      </c>
-      <c r="B59" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C59">
         <v>32</v>
@@ -2011,12 +2011,12 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" t="str">
+        <f>VLOOKUP(B60,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B60" t="s">
         <v>19</v>
-      </c>
-      <c r="B60" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C60">
         <v>32</v>
@@ -2032,12 +2032,12 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" t="str">
+        <f>VLOOKUP(B61,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B61" t="s">
         <v>19</v>
-      </c>
-      <c r="B61" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C61">
         <v>32</v>
@@ -2053,12 +2053,12 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" t="str">
+        <f>VLOOKUP(B62,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B62" t="s">
         <v>19</v>
-      </c>
-      <c r="B62" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C62">
         <v>32</v>
@@ -2074,12 +2074,12 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" t="str">
+        <f>VLOOKUP(B63,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B63" t="s">
         <v>19</v>
-      </c>
-      <c r="B63" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C63">
         <v>32</v>
@@ -2095,12 +2095,12 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" t="str">
+        <f>VLOOKUP(B64,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B64" t="s">
         <v>19</v>
-      </c>
-      <c r="B64" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C64">
         <v>32</v>
@@ -2116,12 +2116,12 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" t="str">
+        <f>VLOOKUP(B65,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B65" t="s">
         <v>19</v>
-      </c>
-      <c r="B65" t="str">
-        <f t="shared" si="0"/>
-        <v>Compressori</v>
       </c>
       <c r="C65">
         <v>32</v>
@@ -2137,12 +2137,12 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" t="str">
+        <f>VLOOKUP(B66,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B66" t="s">
         <v>27</v>
-      </c>
-      <c r="B66" t="str">
-        <f t="shared" si="0"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C66">
         <v>35</v>
@@ -2158,12 +2158,12 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" t="str">
+        <f>VLOOKUP(B67,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B67" t="s">
         <v>27</v>
-      </c>
-      <c r="B67" t="str">
-        <f t="shared" ref="B67:B130" si="2">VLOOKUP(A67,$I$1:$J$26,2,FALSE)</f>
-        <v>Aspiratori</v>
       </c>
       <c r="C67">
         <v>35</v>
@@ -2179,12 +2179,12 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" t="str">
+        <f>VLOOKUP(B68,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B68" t="s">
         <v>27</v>
-      </c>
-      <c r="B68" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C68">
         <v>35</v>
@@ -2200,12 +2200,12 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" t="str">
+        <f>VLOOKUP(B69,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B69" t="s">
         <v>27</v>
-      </c>
-      <c r="B69" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C69">
         <v>35</v>
@@ -2221,12 +2221,12 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" t="str">
+        <f>VLOOKUP(B70,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B70" t="s">
         <v>27</v>
-      </c>
-      <c r="B70" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C70">
         <v>35</v>
@@ -2242,12 +2242,12 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" t="str">
+        <f>VLOOKUP(B71,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B71" t="s">
         <v>27</v>
-      </c>
-      <c r="B71" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C71">
         <v>35</v>
@@ -2263,12 +2263,12 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" t="str">
+        <f>VLOOKUP(B72,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B72" t="s">
         <v>27</v>
-      </c>
-      <c r="B72" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C72">
         <v>35</v>
@@ -2284,12 +2284,12 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" t="str">
+        <f>VLOOKUP(B73,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B73" t="s">
         <v>27</v>
-      </c>
-      <c r="B73" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C73">
         <v>35</v>
@@ -2305,12 +2305,12 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" t="str">
+        <f>VLOOKUP(B74,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B74" t="s">
         <v>24</v>
-      </c>
-      <c r="B74" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C74">
         <v>37</v>
@@ -2326,12 +2326,12 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" t="str">
+        <f>VLOOKUP(B75,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B75" t="s">
         <v>24</v>
-      </c>
-      <c r="B75" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C75">
         <v>37</v>
@@ -2347,12 +2347,12 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" t="str">
+        <f>VLOOKUP(B76,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B76" t="s">
         <v>24</v>
-      </c>
-      <c r="B76" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C76">
         <v>37</v>
@@ -2368,12 +2368,12 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" t="str">
+        <f>VLOOKUP(B77,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B77" t="s">
         <v>24</v>
-      </c>
-      <c r="B77" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C77">
         <v>37</v>
@@ -2389,12 +2389,12 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" t="str">
+        <f>VLOOKUP(B78,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B78" t="s">
         <v>24</v>
-      </c>
-      <c r="B78" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C78">
         <v>37</v>
@@ -2410,12 +2410,12 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" t="str">
+        <f>VLOOKUP(B79,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B79" t="s">
         <v>24</v>
-      </c>
-      <c r="B79" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C79">
         <v>37</v>
@@ -2431,12 +2431,12 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" t="str">
+        <f>VLOOKUP(B80,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B80" t="s">
         <v>24</v>
-      </c>
-      <c r="B80" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C80">
         <v>37</v>
@@ -2452,12 +2452,12 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" t="str">
+        <f>VLOOKUP(B81,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B81" t="s">
         <v>24</v>
-      </c>
-      <c r="B81" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C81">
         <v>37</v>
@@ -2473,12 +2473,12 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" t="str">
+        <f>VLOOKUP(B82,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B82" t="s">
         <v>6</v>
-      </c>
-      <c r="B82" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C82">
         <v>38</v>
@@ -2494,12 +2494,12 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" t="str">
+        <f>VLOOKUP(B83,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B83" t="s">
         <v>6</v>
-      </c>
-      <c r="B83" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C83">
         <v>38</v>
@@ -2515,12 +2515,12 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" t="str">
+        <f>VLOOKUP(B84,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B84" t="s">
         <v>6</v>
-      </c>
-      <c r="B84" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C84">
         <v>38</v>
@@ -2536,12 +2536,12 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" t="str">
+        <f>VLOOKUP(B85,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B85" t="s">
         <v>6</v>
-      </c>
-      <c r="B85" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C85">
         <v>38</v>
@@ -2557,12 +2557,12 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" t="str">
+        <f>VLOOKUP(B86,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B86" t="s">
         <v>6</v>
-      </c>
-      <c r="B86" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C86">
         <v>38</v>
@@ -2578,12 +2578,12 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" t="str">
+        <f>VLOOKUP(B87,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B87" t="s">
         <v>6</v>
-      </c>
-      <c r="B87" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C87">
         <v>38</v>
@@ -2599,12 +2599,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" t="str">
+        <f>VLOOKUP(B88,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B88" t="s">
         <v>6</v>
-      </c>
-      <c r="B88" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C88">
         <v>38</v>
@@ -2620,12 +2620,12 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" t="str">
+        <f>VLOOKUP(B89,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B89" t="s">
         <v>6</v>
-      </c>
-      <c r="B89" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C89">
         <v>38</v>
@@ -2641,12 +2641,12 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" t="str">
+        <f>VLOOKUP(B90,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B90" t="s">
         <v>17</v>
-      </c>
-      <c r="B90" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C90">
         <v>38</v>
@@ -2662,12 +2662,12 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" t="str">
+        <f>VLOOKUP(B91,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B91" t="s">
         <v>17</v>
-      </c>
-      <c r="B91" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C91">
         <v>38</v>
@@ -2683,12 +2683,12 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" t="str">
+        <f>VLOOKUP(B92,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B92" t="s">
         <v>17</v>
-      </c>
-      <c r="B92" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C92">
         <v>38</v>
@@ -2704,12 +2704,12 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" t="str">
+        <f>VLOOKUP(B93,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B93" t="s">
         <v>17</v>
-      </c>
-      <c r="B93" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C93">
         <v>38</v>
@@ -2725,12 +2725,12 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="A94" t="str">
+        <f>VLOOKUP(B94,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B94" t="s">
         <v>17</v>
-      </c>
-      <c r="B94" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C94">
         <v>38</v>
@@ -2746,12 +2746,12 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" t="str">
+        <f>VLOOKUP(B95,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B95" t="s">
         <v>17</v>
-      </c>
-      <c r="B95" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C95">
         <v>38</v>
@@ -2767,12 +2767,12 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" t="str">
+        <f>VLOOKUP(B96,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B96" t="s">
         <v>17</v>
-      </c>
-      <c r="B96" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C96">
         <v>38</v>
@@ -2788,12 +2788,12 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" t="str">
+        <f>VLOOKUP(B97,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B97" t="s">
         <v>17</v>
-      </c>
-      <c r="B97" t="str">
-        <f t="shared" si="2"/>
-        <v>Pompe</v>
       </c>
       <c r="C97">
         <v>38</v>
@@ -2809,12 +2809,12 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" t="str">
+        <f>VLOOKUP(B98,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B98" t="s">
         <v>26</v>
-      </c>
-      <c r="B98" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C98">
         <v>38</v>
@@ -2830,12 +2830,12 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" t="str">
+        <f>VLOOKUP(B99,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B99" t="s">
         <v>26</v>
-      </c>
-      <c r="B99" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C99">
         <v>38</v>
@@ -2851,12 +2851,12 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" t="str">
+        <f>VLOOKUP(B100,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B100" t="s">
         <v>26</v>
-      </c>
-      <c r="B100" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C100">
         <v>38</v>
@@ -2872,12 +2872,12 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" t="str">
+        <f>VLOOKUP(B101,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B101" t="s">
         <v>26</v>
-      </c>
-      <c r="B101" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C101">
         <v>38</v>
@@ -2893,12 +2893,12 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" t="str">
+        <f>VLOOKUP(B102,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B102" t="s">
         <v>26</v>
-      </c>
-      <c r="B102" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C102">
         <v>38</v>
@@ -2914,12 +2914,12 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" t="str">
+        <f>VLOOKUP(B103,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B103" t="s">
         <v>26</v>
-      </c>
-      <c r="B103" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C103">
         <v>38</v>
@@ -2935,12 +2935,12 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" t="str">
+        <f>VLOOKUP(B104,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B104" t="s">
         <v>26</v>
-      </c>
-      <c r="B104" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C104">
         <v>38</v>
@@ -2956,12 +2956,12 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="A105" t="str">
+        <f>VLOOKUP(B105,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B105" t="s">
         <v>26</v>
-      </c>
-      <c r="B105" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C105">
         <v>38</v>
@@ -2977,12 +2977,12 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="A106" t="str">
+        <f>VLOOKUP(B106,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B106" t="s">
         <v>11</v>
-      </c>
-      <c r="B106" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C106">
         <v>40</v>
@@ -2998,12 +2998,12 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="A107" t="str">
+        <f>VLOOKUP(B107,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B107" t="s">
         <v>11</v>
-      </c>
-      <c r="B107" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C107">
         <v>40</v>
@@ -3019,12 +3019,12 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="A108" t="str">
+        <f>VLOOKUP(B108,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B108" t="s">
         <v>11</v>
-      </c>
-      <c r="B108" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C108">
         <v>40</v>
@@ -3040,12 +3040,12 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="A109" t="str">
+        <f>VLOOKUP(B109,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B109" t="s">
         <v>11</v>
-      </c>
-      <c r="B109" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C109">
         <v>40</v>
@@ -3061,12 +3061,12 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="A110" t="str">
+        <f>VLOOKUP(B110,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B110" t="s">
         <v>11</v>
-      </c>
-      <c r="B110" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C110">
         <v>40</v>
@@ -3082,12 +3082,12 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="A111" t="str">
+        <f>VLOOKUP(B111,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B111" t="s">
         <v>11</v>
-      </c>
-      <c r="B111" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C111">
         <v>40</v>
@@ -3103,12 +3103,12 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="A112" t="str">
+        <f>VLOOKUP(B112,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B112" t="s">
         <v>11</v>
-      </c>
-      <c r="B112" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C112">
         <v>40</v>
@@ -3124,12 +3124,12 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="A113" t="str">
+        <f>VLOOKUP(B113,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B113" t="s">
         <v>11</v>
-      </c>
-      <c r="B113" t="str">
-        <f t="shared" si="2"/>
-        <v>Trapani</v>
       </c>
       <c r="C113">
         <v>40</v>
@@ -3145,12 +3145,12 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="A114" t="str">
+        <f>VLOOKUP(B114,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B114" t="s">
         <v>3</v>
-      </c>
-      <c r="B114" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C114">
         <v>45</v>
@@ -3166,12 +3166,12 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="A115" t="str">
+        <f>VLOOKUP(B115,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B115" t="s">
         <v>3</v>
-      </c>
-      <c r="B115" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C115">
         <v>45</v>
@@ -3187,12 +3187,12 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="A116" t="str">
+        <f>VLOOKUP(B116,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B116" t="s">
         <v>3</v>
-      </c>
-      <c r="B116" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C116">
         <v>45</v>
@@ -3208,12 +3208,12 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="A117" t="str">
+        <f>VLOOKUP(B117,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B117" t="s">
         <v>3</v>
-      </c>
-      <c r="B117" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C117">
         <v>45</v>
@@ -3229,12 +3229,12 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="A118" t="str">
+        <f>VLOOKUP(B118,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B118" t="s">
         <v>3</v>
-      </c>
-      <c r="B118" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C118">
         <v>45</v>
@@ -3250,12 +3250,12 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="A119" t="str">
+        <f>VLOOKUP(B119,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B119" t="s">
         <v>3</v>
-      </c>
-      <c r="B119" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C119">
         <v>45</v>
@@ -3271,12 +3271,12 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="A120" t="str">
+        <f>VLOOKUP(B120,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B120" t="s">
         <v>3</v>
-      </c>
-      <c r="B120" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C120">
         <v>45</v>
@@ -3292,12 +3292,12 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="A121" t="str">
+        <f>VLOOKUP(B121,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B121" t="s">
         <v>3</v>
-      </c>
-      <c r="B121" t="str">
-        <f t="shared" si="2"/>
-        <v>Compressori</v>
       </c>
       <c r="C121">
         <v>45</v>
@@ -3313,12 +3313,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="A122" t="str">
+        <f>VLOOKUP(B122,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B122" t="s">
         <v>7</v>
-      </c>
-      <c r="B122" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C122">
         <v>45</v>
@@ -3334,12 +3334,12 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="A123" t="str">
+        <f>VLOOKUP(B123,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B123" t="s">
         <v>7</v>
-      </c>
-      <c r="B123" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C123">
         <v>45</v>
@@ -3355,12 +3355,12 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="A124" t="str">
+        <f>VLOOKUP(B124,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B124" t="s">
         <v>7</v>
-      </c>
-      <c r="B124" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C124">
         <v>45</v>
@@ -3376,12 +3376,12 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="A125" t="str">
+        <f>VLOOKUP(B125,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B125" t="s">
         <v>7</v>
-      </c>
-      <c r="B125" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C125">
         <v>45</v>
@@ -3397,12 +3397,12 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="A126" t="str">
+        <f>VLOOKUP(B126,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B126" t="s">
         <v>7</v>
-      </c>
-      <c r="B126" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C126">
         <v>45</v>
@@ -3418,12 +3418,12 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="A127" t="str">
+        <f>VLOOKUP(B127,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B127" t="s">
         <v>7</v>
-      </c>
-      <c r="B127" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C127">
         <v>45</v>
@@ -3439,12 +3439,12 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" t="str">
+        <f>VLOOKUP(B128,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B128" t="s">
         <v>7</v>
-      </c>
-      <c r="B128" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C128">
         <v>45</v>
@@ -3460,12 +3460,12 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="A129" t="str">
+        <f>VLOOKUP(B129,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B129" t="s">
         <v>7</v>
-      </c>
-      <c r="B129" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C129">
         <v>45</v>
@@ -3481,12 +3481,12 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="A130" t="str">
+        <f>VLOOKUP(B130,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B130" t="s">
         <v>18</v>
-      </c>
-      <c r="B130" t="str">
-        <f t="shared" si="2"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C130">
         <v>45</v>
@@ -3502,12 +3502,12 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="A131" t="str">
+        <f>VLOOKUP(B131,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B131" t="s">
         <v>18</v>
-      </c>
-      <c r="B131" t="str">
-        <f t="shared" ref="B131:B194" si="3">VLOOKUP(A131,$I$1:$J$26,2,FALSE)</f>
-        <v>Aspiratori</v>
       </c>
       <c r="C131">
         <v>45</v>
@@ -3523,12 +3523,12 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="A132" t="str">
+        <f>VLOOKUP(B132,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B132" t="s">
         <v>18</v>
-      </c>
-      <c r="B132" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C132">
         <v>45</v>
@@ -3544,12 +3544,12 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="A133" t="str">
+        <f>VLOOKUP(B133,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B133" t="s">
         <v>18</v>
-      </c>
-      <c r="B133" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C133">
         <v>45</v>
@@ -3565,12 +3565,12 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="A134" t="str">
+        <f>VLOOKUP(B134,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B134" t="s">
         <v>18</v>
-      </c>
-      <c r="B134" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C134">
         <v>45</v>
@@ -3586,12 +3586,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="A135" t="str">
+        <f>VLOOKUP(B135,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B135" t="s">
         <v>18</v>
-      </c>
-      <c r="B135" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C135">
         <v>45</v>
@@ -3607,12 +3607,12 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="A136" t="str">
+        <f>VLOOKUP(B136,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B136" t="s">
         <v>18</v>
-      </c>
-      <c r="B136" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C136">
         <v>45</v>
@@ -3628,12 +3628,12 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="A137" t="str">
+        <f>VLOOKUP(B137,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B137" t="s">
         <v>18</v>
-      </c>
-      <c r="B137" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C137">
         <v>45</v>
@@ -3649,12 +3649,12 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="A138" t="str">
+        <f>VLOOKUP(B138,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B138" t="s">
         <v>2</v>
-      </c>
-      <c r="B138" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C138">
         <v>48</v>
@@ -3670,12 +3670,12 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="A139" t="str">
+        <f>VLOOKUP(B139,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B139" t="s">
         <v>2</v>
-      </c>
-      <c r="B139" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C139">
         <v>48</v>
@@ -3691,12 +3691,12 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="A140" t="str">
+        <f>VLOOKUP(B140,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B140" t="s">
         <v>2</v>
-      </c>
-      <c r="B140" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C140">
         <v>48</v>
@@ -3712,12 +3712,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="A141" t="str">
+        <f>VLOOKUP(B141,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B141" t="s">
         <v>2</v>
-      </c>
-      <c r="B141" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C141">
         <v>48</v>
@@ -3733,12 +3733,12 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A142" t="str">
+        <f>VLOOKUP(B142,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B142" t="s">
         <v>2</v>
-      </c>
-      <c r="B142" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C142">
         <v>48</v>
@@ -3754,12 +3754,12 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="A143" t="str">
+        <f>VLOOKUP(B143,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B143" t="s">
         <v>2</v>
-      </c>
-      <c r="B143" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C143">
         <v>48</v>
@@ -3775,12 +3775,12 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="A144" t="str">
+        <f>VLOOKUP(B144,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B144" t="s">
         <v>2</v>
-      </c>
-      <c r="B144" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C144">
         <v>48</v>
@@ -3796,12 +3796,12 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" t="str">
+        <f>VLOOKUP(B145,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B145" t="s">
         <v>2</v>
-      </c>
-      <c r="B145" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C145">
         <v>48</v>
@@ -3817,12 +3817,12 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" t="str">
+        <f>VLOOKUP(B146,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B146" t="s">
         <v>25</v>
-      </c>
-      <c r="B146" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C146">
         <v>51</v>
@@ -3838,12 +3838,12 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" t="str">
+        <f>VLOOKUP(B147,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B147" t="s">
         <v>25</v>
-      </c>
-      <c r="B147" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C147">
         <v>51</v>
@@ -3859,12 +3859,12 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" t="str">
+        <f>VLOOKUP(B148,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B148" t="s">
         <v>25</v>
-      </c>
-      <c r="B148" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C148">
         <v>51</v>
@@ -3880,12 +3880,12 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" t="str">
+        <f>VLOOKUP(B149,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B149" t="s">
         <v>25</v>
-      </c>
-      <c r="B149" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C149">
         <v>51</v>
@@ -3901,12 +3901,12 @@
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" t="str">
+        <f>VLOOKUP(B150,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B150" t="s">
         <v>25</v>
-      </c>
-      <c r="B150" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C150">
         <v>51</v>
@@ -3922,12 +3922,12 @@
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" t="str">
+        <f>VLOOKUP(B151,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B151" t="s">
         <v>25</v>
-      </c>
-      <c r="B151" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C151">
         <v>51</v>
@@ -3943,12 +3943,12 @@
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" t="str">
+        <f>VLOOKUP(B152,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B152" t="s">
         <v>25</v>
-      </c>
-      <c r="B152" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C152">
         <v>51</v>
@@ -3964,12 +3964,12 @@
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" t="str">
+        <f>VLOOKUP(B153,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B153" t="s">
         <v>25</v>
-      </c>
-      <c r="B153" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C153">
         <v>51</v>
@@ -3985,12 +3985,12 @@
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" t="str">
+        <f>VLOOKUP(B154,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B154" t="s">
         <v>1</v>
-      </c>
-      <c r="B154" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C154">
         <v>57</v>
@@ -4006,12 +4006,12 @@
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" t="str">
+        <f>VLOOKUP(B155,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B155" t="s">
         <v>1</v>
-      </c>
-      <c r="B155" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C155">
         <v>57</v>
@@ -4027,12 +4027,12 @@
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" t="str">
+        <f>VLOOKUP(B156,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B156" t="s">
         <v>1</v>
-      </c>
-      <c r="B156" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C156">
         <v>57</v>
@@ -4048,12 +4048,12 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" t="str">
+        <f>VLOOKUP(B157,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B157" t="s">
         <v>1</v>
-      </c>
-      <c r="B157" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C157">
         <v>57</v>
@@ -4069,12 +4069,12 @@
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" t="str">
+        <f>VLOOKUP(B158,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B158" t="s">
         <v>1</v>
-      </c>
-      <c r="B158" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C158">
         <v>57</v>
@@ -4090,12 +4090,12 @@
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" t="str">
+        <f>VLOOKUP(B159,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B159" t="s">
         <v>1</v>
-      </c>
-      <c r="B159" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C159">
         <v>57</v>
@@ -4111,12 +4111,12 @@
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" t="str">
+        <f>VLOOKUP(B160,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B160" t="s">
         <v>1</v>
-      </c>
-      <c r="B160" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C160">
         <v>57</v>
@@ -4132,12 +4132,12 @@
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" t="str">
+        <f>VLOOKUP(B161,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B161" t="s">
         <v>1</v>
-      </c>
-      <c r="B161" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C161">
         <v>57</v>
@@ -4153,12 +4153,12 @@
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" t="str">
+        <f>VLOOKUP(B162,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B162" t="s">
         <v>16</v>
-      </c>
-      <c r="B162" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C162">
         <v>65</v>
@@ -4174,12 +4174,12 @@
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" t="str">
+        <f>VLOOKUP(B163,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B163" t="s">
         <v>16</v>
-      </c>
-      <c r="B163" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C163">
         <v>65</v>
@@ -4195,12 +4195,12 @@
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" t="str">
+        <f>VLOOKUP(B164,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B164" t="s">
         <v>16</v>
-      </c>
-      <c r="B164" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C164">
         <v>65</v>
@@ -4216,12 +4216,12 @@
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" t="str">
+        <f>VLOOKUP(B165,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B165" t="s">
         <v>16</v>
-      </c>
-      <c r="B165" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C165">
         <v>65</v>
@@ -4237,12 +4237,12 @@
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" t="str">
+        <f>VLOOKUP(B166,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B166" t="s">
         <v>16</v>
-      </c>
-      <c r="B166" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C166">
         <v>65</v>
@@ -4258,12 +4258,12 @@
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" t="str">
+        <f>VLOOKUP(B167,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B167" t="s">
         <v>16</v>
-      </c>
-      <c r="B167" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C167">
         <v>65</v>
@@ -4279,12 +4279,12 @@
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" t="str">
+        <f>VLOOKUP(B168,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B168" t="s">
         <v>16</v>
-      </c>
-      <c r="B168" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C168">
         <v>65</v>
@@ -4300,12 +4300,12 @@
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" t="str">
+        <f>VLOOKUP(B169,$I$1:$J$26,2,FALSE)</f>
+        <v>Compressori</v>
+      </c>
+      <c r="B169" t="s">
         <v>16</v>
-      </c>
-      <c r="B169" t="str">
-        <f t="shared" si="3"/>
-        <v>Compressori</v>
       </c>
       <c r="C169">
         <v>65</v>
@@ -4321,12 +4321,12 @@
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" t="str">
+        <f>VLOOKUP(B170,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B170" t="s">
         <v>10</v>
-      </c>
-      <c r="B170" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C170">
         <v>68</v>
@@ -4342,12 +4342,12 @@
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="A171" t="str">
+        <f>VLOOKUP(B171,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B171" t="s">
         <v>10</v>
-      </c>
-      <c r="B171" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C171">
         <v>68</v>
@@ -4363,12 +4363,12 @@
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="A172" t="str">
+        <f>VLOOKUP(B172,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B172" t="s">
         <v>10</v>
-      </c>
-      <c r="B172" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C172">
         <v>68</v>
@@ -4384,12 +4384,12 @@
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="A173" t="str">
+        <f>VLOOKUP(B173,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B173" t="s">
         <v>10</v>
-      </c>
-      <c r="B173" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C173">
         <v>68</v>
@@ -4405,12 +4405,12 @@
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="A174" t="str">
+        <f>VLOOKUP(B174,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B174" t="s">
         <v>10</v>
-      </c>
-      <c r="B174" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C174">
         <v>68</v>
@@ -4426,12 +4426,12 @@
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="A175" t="str">
+        <f>VLOOKUP(B175,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B175" t="s">
         <v>10</v>
-      </c>
-      <c r="B175" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C175">
         <v>68</v>
@@ -4447,12 +4447,12 @@
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
+      <c r="A176" t="str">
+        <f>VLOOKUP(B176,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B176" t="s">
         <v>10</v>
-      </c>
-      <c r="B176" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C176">
         <v>68</v>
@@ -4468,12 +4468,12 @@
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" t="str">
+        <f>VLOOKUP(B177,$I$1:$J$26,2,FALSE)</f>
+        <v>Trapani</v>
+      </c>
+      <c r="B177" t="s">
         <v>10</v>
-      </c>
-      <c r="B177" t="str">
-        <f t="shared" si="3"/>
-        <v>Trapani</v>
       </c>
       <c r="C177">
         <v>68</v>
@@ -4489,12 +4489,12 @@
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" t="str">
+        <f>VLOOKUP(B178,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B178" t="s">
         <v>8</v>
-      </c>
-      <c r="B178" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C178">
         <v>70</v>
@@ -4510,12 +4510,12 @@
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" t="str">
+        <f>VLOOKUP(B179,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B179" t="s">
         <v>8</v>
-      </c>
-      <c r="B179" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C179">
         <v>70</v>
@@ -4531,12 +4531,12 @@
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" t="str">
+        <f>VLOOKUP(B180,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B180" t="s">
         <v>8</v>
-      </c>
-      <c r="B180" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C180">
         <v>70</v>
@@ -4552,12 +4552,12 @@
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" t="str">
+        <f>VLOOKUP(B181,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B181" t="s">
         <v>8</v>
-      </c>
-      <c r="B181" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C181">
         <v>70</v>
@@ -4573,12 +4573,12 @@
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" t="str">
+        <f>VLOOKUP(B182,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B182" t="s">
         <v>8</v>
-      </c>
-      <c r="B182" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C182">
         <v>70</v>
@@ -4594,12 +4594,12 @@
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" t="str">
+        <f>VLOOKUP(B183,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B183" t="s">
         <v>8</v>
-      </c>
-      <c r="B183" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C183">
         <v>70</v>
@@ -4615,12 +4615,12 @@
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" t="str">
+        <f>VLOOKUP(B184,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B184" t="s">
         <v>8</v>
-      </c>
-      <c r="B184" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C184">
         <v>70</v>
@@ -4636,12 +4636,12 @@
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" t="str">
+        <f>VLOOKUP(B185,$I$1:$J$26,2,FALSE)</f>
+        <v>Aspiratori</v>
+      </c>
+      <c r="B185" t="s">
         <v>8</v>
-      </c>
-      <c r="B185" t="str">
-        <f t="shared" si="3"/>
-        <v>Aspiratori</v>
       </c>
       <c r="C185">
         <v>70</v>
@@ -4657,12 +4657,12 @@
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" t="str">
+        <f>VLOOKUP(B186,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B186" t="s">
         <v>4</v>
-      </c>
-      <c r="B186" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C186">
         <v>103</v>
@@ -4678,12 +4678,12 @@
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" t="str">
+        <f>VLOOKUP(B187,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B187" t="s">
         <v>4</v>
-      </c>
-      <c r="B187" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C187">
         <v>103</v>
@@ -4699,12 +4699,12 @@
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A188" t="str">
+        <f>VLOOKUP(B188,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B188" t="s">
         <v>4</v>
-      </c>
-      <c r="B188" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C188">
         <v>103</v>
@@ -4720,12 +4720,12 @@
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" t="str">
+        <f>VLOOKUP(B189,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B189" t="s">
         <v>4</v>
-      </c>
-      <c r="B189" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C189">
         <v>103</v>
@@ -4741,12 +4741,12 @@
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" t="str">
+        <f>VLOOKUP(B190,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B190" t="s">
         <v>4</v>
-      </c>
-      <c r="B190" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C190">
         <v>103</v>
@@ -4762,12 +4762,12 @@
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
+      <c r="A191" t="str">
+        <f>VLOOKUP(B191,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B191" t="s">
         <v>4</v>
-      </c>
-      <c r="B191" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C191">
         <v>103</v>
@@ -4783,12 +4783,12 @@
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
+      <c r="A192" t="str">
+        <f>VLOOKUP(B192,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B192" t="s">
         <v>4</v>
-      </c>
-      <c r="B192" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C192">
         <v>103</v>
@@ -4804,12 +4804,12 @@
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
+      <c r="A193" t="str">
+        <f>VLOOKUP(B193,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B193" t="s">
         <v>4</v>
-      </c>
-      <c r="B193" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C193">
         <v>103</v>
@@ -4825,12 +4825,12 @@
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
+      <c r="A194" t="str">
+        <f>VLOOKUP(B194,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B194" t="s">
         <v>9</v>
-      </c>
-      <c r="B194" t="str">
-        <f t="shared" si="3"/>
-        <v>Pompe</v>
       </c>
       <c r="C194">
         <v>120</v>
@@ -4846,12 +4846,12 @@
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
+      <c r="A195" t="str">
+        <f>VLOOKUP(B195,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B195" t="s">
         <v>9</v>
-      </c>
-      <c r="B195" t="str">
-        <f t="shared" ref="B195:B201" si="4">VLOOKUP(A195,$I$1:$J$26,2,FALSE)</f>
-        <v>Pompe</v>
       </c>
       <c r="C195">
         <v>120</v>
@@ -4867,12 +4867,12 @@
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
+      <c r="A196" t="str">
+        <f>VLOOKUP(B196,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B196" t="s">
         <v>9</v>
-      </c>
-      <c r="B196" t="str">
-        <f t="shared" si="4"/>
-        <v>Pompe</v>
       </c>
       <c r="C196">
         <v>120</v>
@@ -4888,12 +4888,12 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
+      <c r="A197" t="str">
+        <f>VLOOKUP(B197,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B197" t="s">
         <v>9</v>
-      </c>
-      <c r="B197" t="str">
-        <f t="shared" si="4"/>
-        <v>Pompe</v>
       </c>
       <c r="C197">
         <v>120</v>
@@ -4909,12 +4909,12 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
+      <c r="A198" t="str">
+        <f>VLOOKUP(B198,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B198" t="s">
         <v>9</v>
-      </c>
-      <c r="B198" t="str">
-        <f t="shared" si="4"/>
-        <v>Pompe</v>
       </c>
       <c r="C198">
         <v>120</v>
@@ -4930,12 +4930,12 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
+      <c r="A199" t="str">
+        <f>VLOOKUP(B199,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B199" t="s">
         <v>9</v>
-      </c>
-      <c r="B199" t="str">
-        <f t="shared" si="4"/>
-        <v>Pompe</v>
       </c>
       <c r="C199">
         <v>120</v>
@@ -4951,12 +4951,12 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
+      <c r="A200" t="str">
+        <f>VLOOKUP(B200,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B200" t="s">
         <v>9</v>
-      </c>
-      <c r="B200" t="str">
-        <f t="shared" si="4"/>
-        <v>Pompe</v>
       </c>
       <c r="C200">
         <v>120</v>
@@ -4972,12 +4972,12 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
+      <c r="A201" t="str">
+        <f>VLOOKUP(B201,$I$1:$J$26,2,FALSE)</f>
+        <v>Pompe</v>
+      </c>
+      <c r="B201" t="s">
         <v>9</v>
-      </c>
-      <c r="B201" t="str">
-        <f t="shared" si="4"/>
-        <v>Pompe</v>
       </c>
       <c r="C201">
         <v>120</v>
